--- a/Aula_12!/planilha_excel.xlsx
+++ b/Aula_12!/planilha_excel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,58 @@
         <v>240</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>paula</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C6" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pedrin</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C7" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>joaa</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>123</v>
+      </c>
+      <c r="C9" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
